--- a/paper_tables/Table_3_Top10_Candidate_Anode_Materials.xlsx
+++ b/paper_tables/Table_3_Top10_Candidate_Anode_Materials.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Top10_Candidates" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Top 10 Anodes" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -465,19 +465,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="23" customWidth="1" min="10" max="10"/>
+    <col width="25" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -488,47 +489,52 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Formula</t>
+          <t>formula</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Eg (eV)</t>
+          <t>chemical_family</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Ef (eV/at)</t>
+          <t>band_gap_pred</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Ehull (eV/at)</t>
+          <t>formation_energy_pred</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>K (GPa)</t>
+          <t>energy_hull_pred</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>G (GPa)</t>
+          <t>bulk_modulus_pred</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>E (GPa)</t>
+          <t>shear_modulus_pred</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Eads (eV)</t>
+          <t>young_modulus_pred</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Score</t>
+          <t>E_ads_DFT_eV_pred</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Anode_Composite_Score</t>
         </is>
       </c>
     </row>
@@ -541,29 +547,34 @@
           <t>C</t>
         </is>
       </c>
-      <c r="C2" s="2" t="n">
-        <v>3.637</v>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Carbides</t>
+        </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.232</v>
+        <v>3.425366502599397</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.163</v>
+        <v>0.268845390378307</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>416.498</v>
+        <v>0.2855883871936509</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>478.419</v>
+        <v>422.6001278216253</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>1023.184</v>
+        <v>476.1999215812596</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>-2.749</v>
+        <v>1036.039907838599</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.762</v>
+        <v>-2.827036280322544</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>0.680537860941794</v>
       </c>
     </row>
     <row r="3">
@@ -572,32 +583,37 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>FeOF</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>0.076</v>
+          <t>NbC</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Carbides</t>
+        </is>
       </c>
       <c r="D3" s="4" t="n">
-        <v>-1.745</v>
+        <v>0.02610552721798894</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>1.233</v>
+        <v>-0.585969330537371</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>164.278</v>
+        <v>3.600219820546926</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>85.78</v>
+        <v>303.1314128591071</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>256.652</v>
+        <v>200.9361775303645</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>-2.046</v>
+        <v>484.7692426461933</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>0.648</v>
+        <v>-1.873782153889381</v>
+      </c>
+      <c r="K3" s="4" t="n">
+        <v>0.6112676892583356</v>
       </c>
     </row>
     <row r="4">
@@ -606,32 +622,37 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>NbC</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>0.034</v>
+          <t>FeOF</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Oxyhalides</t>
+        </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>-0.569</v>
+        <v>-0.006746342039259091</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>3.544</v>
+        <v>-1.510969024956381</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>305.343</v>
+        <v>1.062837773105982</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>201.894</v>
+        <v>173.2799773714761</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>489.912</v>
+        <v>88.57512382596462</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>-1.759</v>
+        <v>241.4022848767369</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.621</v>
+        <v>-2.17039731520575</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>0.6037943450111416</v>
       </c>
     </row>
     <row r="5">
@@ -640,32 +661,37 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>NbF3</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>0</v>
+          <t>Rb2F</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Halides</t>
+        </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>-2.766</v>
+        <v>0.05132674331133561</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.591</v>
+        <v>-1.792209184770039</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>98.117</v>
+        <v>-0.05337705552464662</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>44.015</v>
+        <v>12.21869874283519</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>98.842</v>
+        <v>2.49626233345292</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>-3.031</v>
+        <v>10.2016208727253</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>0.593</v>
+        <v>-1.883647252843469</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>0.5740471974797962</v>
       </c>
     </row>
     <row r="6">
@@ -674,32 +700,37 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Rb2F</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>0</v>
+          <t>CuMoO4</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Oxides</t>
+        </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>-1.829</v>
+        <v>-0.05017570435845366</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0</v>
+        <v>-1.671529083826328</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>8.215999999999999</v>
+        <v>2.642174935186469</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>3.726</v>
+        <v>133.6924531964758</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>12.531</v>
+        <v>56.8612101831671</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>-2.078</v>
+        <v>158.197220336822</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.592</v>
+        <v>-2.146431567075587</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>0.5484811576407644</v>
       </c>
     </row>
     <row r="7">
@@ -708,32 +739,37 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Mn2F7</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>0.173</v>
+          <t>NbF3</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Halides</t>
+        </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-2.008</v>
+        <v>0.1030999522495951</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.717</v>
+        <v>-2.70096631301255</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>42.39</v>
+        <v>0.5932897175494903</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>20.732</v>
+        <v>93.56004512147122</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>43.609</v>
+        <v>44.84041419018576</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-2.464</v>
+        <v>113.6381636232273</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.587</v>
+        <v>-3.012905813603394</v>
+      </c>
+      <c r="K7" s="4" t="n">
+        <v>0.5395762787440281</v>
       </c>
     </row>
     <row r="8">
@@ -745,29 +781,34 @@
           <t>HoBrO</t>
         </is>
       </c>
-      <c r="C8" s="2" t="n">
-        <v>3.833</v>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Oxyhalides</t>
+        </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>-3.021</v>
+        <v>3.717023979623296</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.062</v>
+        <v>-3.26913121540734</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>60.826</v>
+        <v>0.06086886544681178</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>29.888</v>
+        <v>47.53048174257501</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>90.383</v>
+        <v>28.56264777287646</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>-2.075</v>
+        <v>69.87816683566626</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.584</v>
+        <v>-2.140709320325295</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>0.538563424471673</v>
       </c>
     </row>
     <row r="9">
@@ -776,32 +817,37 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>CuMoO4</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>0</v>
+          <t>Mn2F7</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Halides</t>
+        </is>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-1.602</v>
+        <v>0.008704706823817123</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>2.602</v>
+        <v>-1.749261480747622</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>132.468</v>
+        <v>0.7662476599776106</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>58.529</v>
+        <v>37.3480952035063</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>141.828</v>
+        <v>20.62288836985503</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-2.115</v>
+        <v>59.08704749630527</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.577</v>
+        <v>-2.576503243560074</v>
+      </c>
+      <c r="K9" s="4" t="n">
+        <v>0.5268093772088573</v>
       </c>
     </row>
     <row r="10">
@@ -810,32 +856,37 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>HgF2</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="n">
-        <v>0.881</v>
+          <t>MnF4</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Halides</t>
+        </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>-1.442</v>
+        <v>0.02613304984009023</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0</v>
+        <v>-2.254908134488431</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>100.376</v>
+        <v>0.3100504943602185</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>27.829</v>
+        <v>51.91203962106388</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>41.21</v>
+        <v>34.11773387165616</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>-2.717</v>
+        <v>76.2989106882623</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.577</v>
+        <v>-3.127771182313201</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>0.5197084350571323</v>
       </c>
     </row>
     <row r="11">
@@ -844,32 +895,37 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>VOF</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>0.701</v>
+          <t>YMg5</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Intermetallics/Alloys</t>
+        </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-2.507</v>
+        <v>-0.1987568914600893</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>1.055</v>
+        <v>0.05451014107945619</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>106.262</v>
+        <v>0.1874434956150345</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>48.83</v>
+        <v>37.48212905308654</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>120.792</v>
+        <v>18.33708394298516</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-2.928</v>
+        <v>45.90234640435155</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.575</v>
+        <v>-2.039870727239029</v>
+      </c>
+      <c r="K11" s="4" t="n">
+        <v>0.5195131573324604</v>
       </c>
     </row>
   </sheetData>
